--- a/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3793" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3793" uniqueCount="555">
   <si>
     <t>Property</t>
   </si>
@@ -747,6 +747,9 @@
     <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -793,6 +796,9 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>procedure</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -946,6 +952,9 @@
     <t>このObservationに関する詳細分類、JP_ObservationDentalCategory_VSより選択する、必須項目</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDentalCategory_VS</t>
+  </si>
+  <si>
     <t>Observation.category:third.id</t>
   </si>
   <si>
@@ -964,10 +973,16 @@
     <t>Observation.category:third.coding.system</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS</t>
+  </si>
+  <si>
     <t>Observation.category:third.coding.version</t>
   </si>
   <si>
     <t>Observation.category:third.coding.code</t>
+  </si>
+  <si>
+    <t>MissingToothCondition</t>
   </si>
   <si>
     <t>Observation.category:third.coding.display</t>
@@ -4624,7 +4639,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -4658,7 +4673,7 @@
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>83</v>
+        <v>234</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4700,7 +4715,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4721,10 +4736,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4735,10 +4750,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4764,13 +4779,13 @@
         <v>203</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4820,7 +4835,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4841,10 +4856,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4855,10 +4870,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4884,21 +4899,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>83</v>
+        <v>251</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4940,7 +4955,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4961,10 +4976,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4975,10 +4990,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5004,14 +5019,14 @@
         <v>203</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5060,7 +5075,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5081,10 +5096,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5095,10 +5110,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5121,19 +5136,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5182,7 +5197,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5203,10 +5218,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5217,10 +5232,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5246,16 +5261,16 @@
         <v>203</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5304,7 +5319,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5325,10 +5340,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5339,13 +5354,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>186</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5370,10 +5385,10 @@
         <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>200</v>
@@ -5461,7 +5476,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>202</v>
@@ -5579,7 +5594,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>209</v>
@@ -5699,7 +5714,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>215</v>
@@ -5821,7 +5836,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>225</v>
@@ -5939,7 +5954,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>227</v>
@@ -6059,7 +6074,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>229</v>
@@ -6104,7 +6119,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6146,7 +6161,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6167,10 +6182,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6181,10 +6196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6210,13 +6225,13 @@
         <v>203</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6266,7 +6281,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6287,10 +6302,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6301,10 +6316,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6330,21 +6345,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6386,7 +6401,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6407,10 +6422,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6421,10 +6436,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6450,14 +6465,14 @@
         <v>203</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6467,7 +6482,7 @@
         <v>83</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>83</v>
@@ -6506,7 +6521,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6527,10 +6542,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6541,10 +6556,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6567,19 +6582,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6628,7 +6643,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6649,10 +6664,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6663,10 +6678,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6692,16 +6707,16 @@
         <v>203</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6750,7 +6765,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6771,10 +6786,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6785,13 +6800,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>186</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -6816,10 +6831,10 @@
         <v>188</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>200</v>
@@ -6850,11 +6865,11 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>192</v>
+        <v>302</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6907,7 +6922,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>202</v>
@@ -7025,7 +7040,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>209</v>
@@ -7145,7 +7160,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>215</v>
@@ -7267,7 +7282,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>225</v>
@@ -7385,7 +7400,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>227</v>
@@ -7505,7 +7520,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>229</v>
@@ -7516,7 +7531,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>94</v>
@@ -7550,7 +7565,7 @@
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7592,7 +7607,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7613,10 +7628,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7627,10 +7642,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7656,13 +7671,13 @@
         <v>203</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7712,7 +7727,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7733,10 +7748,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7747,10 +7762,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7776,21 +7791,21 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>83</v>
+        <v>312</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -7832,7 +7847,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7853,10 +7868,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7867,10 +7882,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7896,14 +7911,14 @@
         <v>203</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7913,7 +7928,7 @@
         <v>83</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>83</v>
@@ -7952,7 +7967,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7973,10 +7988,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7987,10 +8002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8013,19 +8028,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8074,7 +8089,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8095,10 +8110,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8109,10 +8124,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8138,16 +8153,16 @@
         <v>203</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8196,7 +8211,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8217,10 +8232,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8231,14 +8246,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8260,16 +8275,16 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8294,31 +8309,31 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8333,30 +8348,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8471,10 +8486,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8591,10 +8606,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8620,10 +8635,10 @@
         <v>216</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>219</v>
@@ -8713,10 +8728,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8831,10 +8846,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8951,10 +8966,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8996,7 +9011,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9038,7 +9053,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9059,10 +9074,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9073,10 +9088,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9102,13 +9117,13 @@
         <v>203</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9158,7 +9173,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9179,10 +9194,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9193,10 +9208,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9222,21 +9237,21 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9278,7 +9293,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9299,10 +9314,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9313,10 +9328,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9342,14 +9357,14 @@
         <v>203</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9359,7 +9374,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9398,7 +9413,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9419,10 +9434,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9433,10 +9448,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9459,19 +9474,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9520,7 +9535,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9541,10 +9556,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9555,10 +9570,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9584,16 +9599,16 @@
         <v>203</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9642,7 +9657,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9663,10 +9678,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9677,10 +9692,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9703,19 +9718,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9764,7 +9779,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9779,19 +9794,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -9799,10 +9814,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9825,7 +9840,7 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>162</v>
@@ -9834,7 +9849,7 @@
         <v>162</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9884,7 +9899,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9905,13 +9920,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -9919,14 +9934,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9945,19 +9960,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10006,7 +10021,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10021,19 +10036,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10041,14 +10056,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10067,19 +10082,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10128,7 +10143,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10143,19 +10158,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10163,10 +10178,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10189,16 +10204,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10248,7 +10263,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10269,13 +10284,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10283,10 +10298,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10309,19 +10324,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10370,7 +10385,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10385,19 +10400,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10405,10 +10420,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10434,16 +10449,16 @@
         <v>188</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10492,7 +10507,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10501,7 +10516,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10510,27 +10525,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10556,16 +10571,16 @@
         <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10590,31 +10605,31 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10623,7 +10638,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10638,7 +10653,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10649,14 +10664,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10684,10 +10699,10 @@
         <v>162</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10712,31 +10727,31 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="Z72" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10754,27 +10769,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10797,7 +10812,7 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>162</v>
@@ -10806,10 +10821,10 @@
         <v>162</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10858,7 +10873,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10879,10 +10894,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10893,10 +10908,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10922,13 +10937,13 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10954,13 +10969,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -10978,7 +10993,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10996,27 +11011,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11042,16 +11057,16 @@
         <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11076,31 +11091,31 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="Z75" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11121,10 +11136,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11135,10 +11150,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11161,7 +11176,7 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>162</v>
@@ -11170,7 +11185,7 @@
         <v>162</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11220,7 +11235,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11238,27 +11253,27 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11281,16 +11296,16 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11340,7 +11355,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11358,27 +11373,27 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11401,7 +11416,7 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>162</v>
@@ -11410,10 +11425,10 @@
         <v>162</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11462,7 +11477,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11474,7 +11489,7 @@
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>83</v>
@@ -11483,10 +11498,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11497,10 +11512,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11615,10 +11630,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11735,14 +11750,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11764,10 +11779,10 @@
         <v>140</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>143</v>
@@ -11822,7 +11837,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11857,10 +11872,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11883,13 +11898,13 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11940,7 +11955,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -11949,7 +11964,7 @@
         <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -11961,10 +11976,10 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -11975,10 +11990,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12001,13 +12016,13 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12058,7 +12073,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12067,7 +12082,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12079,10 +12094,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12093,10 +12108,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12122,16 +12137,16 @@
         <v>188</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12159,28 +12174,28 @@
         <v>118</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12198,13 +12213,13 @@
         <v>83</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12215,10 +12230,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12244,16 +12259,16 @@
         <v>188</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12278,31 +12293,31 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12320,13 +12335,13 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12337,10 +12352,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12363,17 +12378,17 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12422,7 +12437,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12446,7 +12461,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12457,10 +12472,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12486,10 +12501,10 @@
         <v>203</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12540,7 +12555,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12561,10 +12576,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12575,10 +12590,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12601,16 +12616,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12660,7 +12675,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12681,10 +12696,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12695,10 +12710,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12721,7 +12736,7 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>162</v>
@@ -12730,7 +12745,7 @@
         <v>162</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12780,7 +12795,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12801,10 +12816,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12815,10 +12830,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12841,19 +12856,19 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -12902,7 +12917,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -12923,10 +12938,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -12937,10 +12952,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13055,10 +13070,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13175,14 +13190,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13204,10 +13219,10 @@
         <v>140</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>143</v>
@@ -13262,7 +13277,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13297,10 +13312,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13326,16 +13341,16 @@
         <v>188</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13360,13 +13375,13 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -13384,7 +13399,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>94</v>
@@ -13402,16 +13417,16 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -13419,10 +13434,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13445,19 +13460,19 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13506,7 +13521,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13524,27 +13539,27 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13570,16 +13585,16 @@
         <v>188</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13604,13 +13619,13 @@
         <v>83</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
@@ -13628,7 +13643,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13637,7 +13652,7 @@
         <v>94</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>106</v>
@@ -13652,7 +13667,7 @@
         <v>137</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13663,14 +13678,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13692,16 +13707,16 @@
         <v>188</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -13726,13 +13741,13 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -13750,7 +13765,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13768,27 +13783,27 @@
         <v>83</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13814,16 +13829,16 @@
         <v>84</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -13872,7 +13887,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13893,10 +13908,10 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
